--- a/data/2025/36-teleorman/151790-alexandria/budget_file.xlsx
+++ b/data/2025/36-teleorman/151790-alexandria/budget_file.xlsx
@@ -1497,7 +1497,7 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>30.02 est2028: parent 1.670,00 != sum(children) 740,00 (2 children); 30.02 est2027: parent 1.670,00 != sum(children) 740,00 (2 children); 30.02 trim4: parent 284,00 != sum(children) 159,00 (2 children); 30.02 total: parent 1.659,00 != sum(children) 734,00 (2 children); 30.02 trim2: parent 525,00 != sum(children) 225,00 (2 children); 30.02 trim3: parent 325,00 != sum(children) 125,00 (2 children); 30.02 trim1: parent 525,00 != sum(children) 225,00 (2 children)</t>
+          <t>30.02 trim2: parent 525,00 != sum(children) 225,00 (2 children); 30.02 trim1: parent 525,00 != sum(children) 225,00 (2 children); 30.02 trim4: parent 284,00 != sum(children) 159,00 (2 children); 30.02 est2028: parent 1.670,00 != sum(children) 740,00 (2 children); 30.02 total: parent 1.659,00 != sum(children) 734,00 (2 children); 30.02 trim3: parent 325,00 != sum(children) 125,00 (2 children); 30.02 est2027: parent 1.670,00 != sum(children) 740,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>42.02 trim4: parent 43.950,70 != sum(children) 43.715,17 (6 children); 42.02 total: parent 166.103,28 != sum(children) 164.067,75 (6 children); 42.02 trim2: parent 49.487,32 != sum(children) 48.887,32 (6 children); 42.02 trim3: parent 45.728,50 != sum(children) 45.228,50 (6 children); 42.02 trim1: parent 26.936,76 != sum(children) 26.236,76 (6 children)</t>
+          <t>42.02 trim2: parent 49.487,32 != sum(children) 48.887,32 (6 children); 42.02 trim1: parent 26.936,76 != sum(children) 26.236,76 (6 children); 42.02 trim4: parent 43.950,70 != sum(children) 43.715,17 (6 children); 42.02 total: parent 166.103,28 != sum(children) 164.067,75 (6 children); 42.02 trim3: parent 45.728,50 != sum(children) 45.228,50 (6 children)</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>45.02 trim4: parent 0,00 != sum(children) 9.107,11 (1 children); 45.02 total: parent 0,00 != sum(children) 39.707,11 (1 children); 45.02 trim2: parent 0,00 != sum(children) 10.200,00 (1 children); 45.02 trim3: parent 0,00 != sum(children) 10.200,00 (1 children); 45.02 trim1: parent 0,00 != sum(children) 10.200,00 (1 children)</t>
+          <t>45.02 trim2: parent 0,00 != sum(children) 10.200,00 (1 children); 45.02 trim1: parent 0,00 != sum(children) 10.200,00 (1 children); 45.02 trim4: parent 0,00 != sum(children) 9.107,11 (1 children); 45.02 total: parent 0,00 != sum(children) 39.707,11 (1 children); 45.02 trim3: parent 0,00 != sum(children) 10.200,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -3558,50 +3558,57 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>51.02</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>AUTORITATI PUBLICE SI ACTIUNI EXTERNE</t>
         </is>
       </c>
-      <c r="E67" t="n">
+      <c r="D67" s="3" t="n"/>
+      <c r="E67" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G67" s="4" t="n">
         <v>18987.4</v>
       </c>
-      <c r="H67" s="2" t="n"/>
-      <c r="I67" s="2" t="n"/>
-      <c r="J67" s="2" t="n">
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="4" t="n"/>
+      <c r="J67" s="4" t="n">
         <v>5355.64</v>
       </c>
-      <c r="K67" s="2" t="n">
+      <c r="K67" s="4" t="n">
         <v>5065.87</v>
       </c>
-      <c r="L67" s="2" t="n">
+      <c r="L67" s="4" t="n">
         <v>4566.37</v>
       </c>
-      <c r="M67" s="2" t="n">
+      <c r="M67" s="4" t="n">
         <v>3999.52</v>
       </c>
-      <c r="N67" s="2" t="n">
+      <c r="N67" s="4" t="n">
         <v>19016</v>
       </c>
-      <c r="O67" s="2" t="n">
+      <c r="O67" s="4" t="n">
         <v>19116</v>
       </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>digital</t>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr">
+        <is>
+          <t>51.02 trim2: parent 5.065,87 != sum(children) 45,00 (1 children); 51.02 trim1: parent 5.355,64 != sum(children) 45,00 (1 children); 51.02 trim4: parent 3.999,52 != sum(children) 36,40 (1 children); 51.02 total: parent 18.987,40 != sum(children) 171,40 (1 children); 51.02 trim3: parent 4.566,37 != sum(children) 45,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4875,7 @@
       </c>
       <c r="Q93" s="3" t="inlineStr">
         <is>
-          <t>20.06 total: parent 30,00 != sum(children) 5,00 (1 children); 20.06 trim2: parent 17,00 != sum(children) 5,00 (1 children)</t>
+          <t>20.06 trim2: parent 17,00 != sum(children) 5,00 (1 children); 20.06 total: parent 30,00 != sum(children) 5,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -5602,52 +5609,59 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>54.02</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="B109" s="3" t="n"/>
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>ALTE SERVICII PUBLICE GENERALE</t>
         </is>
       </c>
-      <c r="E109" t="n">
+      <c r="D109" s="3" t="n"/>
+      <c r="E109" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F109" s="3" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G109" s="2" t="n">
+      <c r="G109" s="4" t="n">
         <v>7690.71</v>
       </c>
-      <c r="H109" s="2" t="n">
+      <c r="H109" s="4" t="n">
         <v>0.55</v>
       </c>
-      <c r="I109" s="2" t="n"/>
-      <c r="J109" s="2" t="n">
+      <c r="I109" s="4" t="n"/>
+      <c r="J109" s="4" t="n">
         <v>2556.5</v>
       </c>
-      <c r="K109" s="2" t="n">
+      <c r="K109" s="4" t="n">
         <v>2596.3</v>
       </c>
-      <c r="L109" s="2" t="n">
+      <c r="L109" s="4" t="n">
         <v>2250.31</v>
       </c>
-      <c r="M109" s="2" t="n">
+      <c r="M109" s="4" t="n">
         <v>287.6</v>
       </c>
-      <c r="N109" s="2" t="n">
+      <c r="N109" s="4" t="n">
         <v>1435</v>
       </c>
-      <c r="O109" s="2" t="n">
+      <c r="O109" s="4" t="n">
         <v>1535</v>
       </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>digital</t>
+      <c r="P109" s="3" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="Q109" s="3" t="inlineStr">
+        <is>
+          <t>54.02 trim2: parent 2.596,30 != sum(children) 7,20 (1 children); 54.02 total: parent 7.690,71 != sum(children) 7,20 (1 children)</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6163,7 @@
       </c>
       <c r="Q119" s="3" t="inlineStr">
         <is>
-          <t>20 total: parent 120,00 != sum(children) 119,00 (5 children); 20 trim1: parent 41,50 != sum(children) 40,50 (5 children)</t>
+          <t>20 trim1: parent 41,50 != sum(children) 40,50 (5 children); 20 total: parent 120,00 != sum(children) 119,00 (5 children)</t>
         </is>
       </c>
     </row>
@@ -7415,50 +7429,57 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="3" t="inlineStr">
         <is>
           <t>61.02</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="B147" s="3" t="n"/>
+      <c r="C147" s="3" t="inlineStr">
         <is>
           <t>ORDINE PUBLICA SI SIGURANTA NATIONALA</t>
         </is>
       </c>
-      <c r="E147" t="n">
+      <c r="D147" s="3" t="n"/>
+      <c r="E147" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="F147" s="3" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G147" s="2" t="n">
+      <c r="G147" s="4" t="n">
         <v>4945.4</v>
       </c>
-      <c r="H147" s="2" t="n"/>
-      <c r="I147" s="2" t="n"/>
-      <c r="J147" s="2" t="n">
+      <c r="H147" s="4" t="n"/>
+      <c r="I147" s="4" t="n"/>
+      <c r="J147" s="4" t="n">
         <v>1406.53</v>
       </c>
-      <c r="K147" s="2" t="n">
+      <c r="K147" s="4" t="n">
         <v>1329.5</v>
       </c>
-      <c r="L147" s="2" t="n">
+      <c r="L147" s="4" t="n">
         <v>1172.9</v>
       </c>
-      <c r="M147" s="2" t="n">
+      <c r="M147" s="4" t="n">
         <v>1036.47</v>
       </c>
-      <c r="N147" s="2" t="n">
+      <c r="N147" s="4" t="n">
         <v>5145</v>
       </c>
-      <c r="O147" s="2" t="n">
+      <c r="O147" s="4" t="n">
         <v>5295</v>
       </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>digital</t>
+      <c r="P147" s="3" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="Q147" s="3" t="inlineStr">
+        <is>
+          <t>61.02 trim2: parent 1.329,50 != sum(children) 36,00 (1 children); 61.02 total: parent 4.945,40 != sum(children) 36,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -7961,51 +7982,57 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="A158" s="3" t="inlineStr">
         <is>
           <t>20.01</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B158" s="3" t="inlineStr">
         <is>
           <t>61.02</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C158" s="3" t="inlineStr">
         <is>
           <t>Bunuri si servicii</t>
         </is>
       </c>
-      <c r="E158" t="n">
+      <c r="D158" s="3" t="n"/>
+      <c r="E158" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="n">
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="n">
         <v>269</v>
       </c>
-      <c r="H158" s="2" t="n"/>
-      <c r="I158" s="2" t="n"/>
-      <c r="J158" s="2" t="n">
+      <c r="H158" s="4" t="n"/>
+      <c r="I158" s="4" t="n"/>
+      <c r="J158" s="4" t="n">
         <v>112.05</v>
       </c>
-      <c r="K158" s="2" t="n">
+      <c r="K158" s="4" t="n">
         <v>80.75</v>
       </c>
-      <c r="L158" s="2" t="n">
+      <c r="L158" s="4" t="n">
         <v>63.75</v>
       </c>
-      <c r="M158" s="2" t="n">
+      <c r="M158" s="4" t="n">
         <v>12.45</v>
       </c>
-      <c r="N158" s="2" t="n"/>
-      <c r="O158" s="2" t="n"/>
-      <c r="P158" t="inlineStr">
-        <is>
-          <t>digital</t>
+      <c r="N158" s="4" t="n"/>
+      <c r="O158" s="4" t="n"/>
+      <c r="P158" s="3" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="Q158" s="3" t="inlineStr">
+        <is>
+          <t>20.01 trim2: parent 80,75 != sum(children) 22,75 (8 children); 20.01 trim1: parent 112,05 != sum(children) 53,95 (8 children); 20.01 trim4: parent 12,45 != sum(children) 2,05 (8 children); 20.01 total: parent 269,00 != sum(children) 87,00 (8 children); 20.01 trim3: parent 63,75 != sum(children) 8,25 (8 children)</t>
         </is>
       </c>
     </row>
@@ -8180,28 +8207,18 @@
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G162" s="2" t="n">
-        <v>182</v>
-      </c>
+      <c r="G162" s="2" t="n"/>
       <c r="H162" s="2" t="n"/>
       <c r="I162" s="2" t="n"/>
-      <c r="J162" s="2" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="K162" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="L162" s="2" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="M162" s="2" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="J162" s="2" t="n"/>
+      <c r="K162" s="2" t="n"/>
+      <c r="L162" s="2" t="n"/>
+      <c r="M162" s="2" t="n"/>
       <c r="N162" s="2" t="n"/>
       <c r="O162" s="2" t="n"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>digital</t>
         </is>
       </c>
     </row>
@@ -8237,20 +8254,14 @@
       <c r="J163" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="K163" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L163" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M163" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K163" s="2" t="n"/>
+      <c r="L163" s="2" t="n"/>
+      <c r="M163" s="2" t="n"/>
       <c r="N163" s="2" t="n"/>
       <c r="O163" s="2" t="n"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>digital</t>
         </is>
       </c>
     </row>
@@ -8292,14 +8303,12 @@
       <c r="L164" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M164" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="M164" s="2" t="n"/>
       <c r="N164" s="2" t="n"/>
       <c r="O164" s="2" t="n"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>digital</t>
         </is>
       </c>
     </row>
@@ -8390,14 +8399,12 @@
       <c r="L166" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="M166" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="M166" s="2" t="n"/>
       <c r="N166" s="2" t="n"/>
       <c r="O166" s="2" t="n"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>digital</t>
         </is>
       </c>
     </row>
@@ -9313,52 +9320,59 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
+      <c r="A187" s="3" t="inlineStr">
         <is>
           <t>65.02</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
+      <c r="B187" s="3" t="n"/>
+      <c r="C187" s="3" t="inlineStr">
         <is>
           <t>INVATAMANT</t>
         </is>
       </c>
-      <c r="E187" t="n">
+      <c r="D187" s="3" t="n"/>
+      <c r="E187" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="F187" t="inlineStr">
+      <c r="F187" s="3" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G187" s="2" t="n">
+      <c r="G187" s="4" t="n">
         <v>30818.07</v>
       </c>
-      <c r="H187" s="2" t="n">
+      <c r="H187" s="4" t="n">
         <v>1835.91</v>
       </c>
-      <c r="I187" s="2" t="n"/>
-      <c r="J187" s="2" t="n">
+      <c r="I187" s="4" t="n"/>
+      <c r="J187" s="4" t="n">
         <v>12164.47</v>
       </c>
-      <c r="K187" s="2" t="n">
+      <c r="K187" s="4" t="n">
         <v>8485.84</v>
       </c>
-      <c r="L187" s="2" t="n">
+      <c r="L187" s="4" t="n">
         <v>5674.92</v>
       </c>
-      <c r="M187" s="2" t="n">
+      <c r="M187" s="4" t="n">
         <v>4492.84</v>
       </c>
-      <c r="N187" s="2" t="n">
+      <c r="N187" s="4" t="n">
         <v>8506.620000000001</v>
       </c>
-      <c r="O187" s="2" t="n">
+      <c r="O187" s="4" t="n">
         <v>8036.62</v>
       </c>
-      <c r="P187" t="inlineStr">
-        <is>
-          <t>digital</t>
+      <c r="P187" s="3" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="Q187" s="3" t="inlineStr">
+        <is>
+          <t>65.02 trim2: parent 8.485,84 != sum(children) 3.307,40 (1 children); 65.02 trim1: parent 12.164,47 != sum(children) 3.350,53 (1 children); 65.02 trim4: parent 4.492,84 != sum(children) 3.041,14 (1 children); 65.02 est2028: parent 8.036,62 != sum(children) 4.595,62 (1 children); 65.02 total: parent 30.818,07 != sum(children) 12.931,96 (1 children); 65.02 trim3: parent 5.674,92 != sum(children) 3.232,89 (1 children); 65.02 est2027: parent 8.506,62 != sum(children) 5.113,62 (1 children)</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9688,7 @@
       </c>
       <c r="Q193" s="3" t="inlineStr">
         <is>
-          <t>20.01 total: parent 3.349,60 != sum(children) 3.222,72 (7 children); 20.01 trim2: parent 38,00 != sum(children) 36,00 (7 children); 20.01 trim3: parent 29,00 != sum(children) 28,00 (7 children); 20.01 trim1: parent 3.274,60 != sum(children) 3.150,72 (7 children)</t>
+          <t>20.01 trim2: parent 38,00 != sum(children) 36,00 (7 children); 20.01 trim1: parent 3.274,60 != sum(children) 3.150,72 (7 children); 20.01 total: parent 3.349,60 != sum(children) 3.222,72 (7 children); 20.01 trim3: parent 29,00 != sum(children) 28,00 (7 children)</t>
         </is>
       </c>
     </row>
@@ -11497,24 +11511,14 @@
       <c r="J232" s="2" t="n">
         <v>122.5</v>
       </c>
-      <c r="K232" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L232" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M232" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N232" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O232" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K232" s="2" t="n"/>
+      <c r="L232" s="2" t="n"/>
+      <c r="M232" s="2" t="n"/>
+      <c r="N232" s="2" t="n"/>
+      <c r="O232" s="2" t="n"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>digital</t>
         </is>
       </c>
     </row>
@@ -12157,7 +12161,7 @@
       </c>
       <c r="Q245" s="3" t="inlineStr">
         <is>
-          <t>20 total: parent 200,00 != sum(children) 190,00 (5 children); 20 trim1: parent 75,40 != sum(children) 74,40 (5 children); 20 trim2: parent 108,60 != sum(children) 99,60 (5 children)</t>
+          <t>20 trim2: parent 108,60 != sum(children) 99,60 (5 children); 20 trim1: parent 75,40 != sum(children) 74,40 (5 children); 20 total: parent 200,00 != sum(children) 190,00 (5 children)</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13031,7 @@
       </c>
       <c r="Q264" s="3" t="inlineStr">
         <is>
-          <t>67.02 est2028: parent 17.470,00 != sum(children) 3.990,00 (3 children); 67.02 est2027: parent 17.180,00 != sum(children) 3.890,00 (3 children); 67.02 trim4: parent 1.404,72 != sum(children) 305,00 (3 children); 67.02 total: parent 16.359,72 != sum(children) 4.235,15 (3 children); 67.02 trim2: parent 6.404,85 != sum(children) 2.151,00 (3 children); 67.02 trim3: parent 2.810,14 != sum(children) 1.216,01 (3 children); 67.02 trim1: parent 5.740,01 != sum(children) 563,14 (3 children); 67.02 trim3: parent 2.810,14 != sum(children) 120,01 (1 children); 67.02 total: parent 16.359,72 != sum(children) 844,15 (1 children); 67.02 trim1: parent 5.740,01 != sum(children) 47,14 (1 children); 67.02 trim2: parent 6.404,85 != sum(children) 677,00 (1 children)</t>
+          <t>67.02 trim2: parent 6.404,85 != sum(children) 2.151,00 (3 children); 67.02 trim1: parent 5.740,01 != sum(children) 563,14 (3 children); 67.02 trim4: parent 1.404,72 != sum(children) 305,00 (3 children); 67.02 est2028: parent 17.470,00 != sum(children) 3.990,00 (3 children); 67.02 total: parent 16.359,72 != sum(children) 4.235,15 (3 children); 67.02 trim3: parent 2.810,14 != sum(children) 1.216,01 (3 children); 67.02 est2027: parent 17.180,00 != sum(children) 3.890,00 (3 children); 67.02 trim2: parent 6.404,85 != sum(children) 677,00 (1 children); 67.02 trim1: parent 5.740,01 != sum(children) 47,14 (1 children); 67.02 trim3: parent 2.810,14 != sum(children) 120,01 (1 children); 67.02 total: parent 16.359,72 != sum(children) 844,15 (1 children)</t>
         </is>
       </c>
     </row>
@@ -15822,7 +15826,7 @@
       </c>
       <c r="Q323" s="3" t="inlineStr">
         <is>
-          <t>20.04 total: parent 29,00 != sum(children) 17,00 (2 children); 20.04 trim1: parent 19,00 != sum(children) 8,00 (2 children); 20.04 trim2: parent 9,00 != sum(children) 8,00 (2 children)</t>
+          <t>20.04 trim2: parent 9,00 != sum(children) 8,00 (2 children); 20.04 trim1: parent 19,00 != sum(children) 8,00 (2 children); 20.04 total: parent 29,00 != sum(children) 17,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -16902,52 +16906,59 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr">
+      <c r="A347" s="3" t="inlineStr">
         <is>
           <t>70.02</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr">
+      <c r="B347" s="3" t="n"/>
+      <c r="C347" s="3" t="inlineStr">
         <is>
           <t>LOCUINTE, SERVICII SI DEZVOLTARE</t>
         </is>
       </c>
-      <c r="E347" t="n">
+      <c r="D347" s="3" t="n"/>
+      <c r="E347" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="F347" t="inlineStr">
+      <c r="F347" s="3" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G347" s="2" t="n">
+      <c r="G347" s="4" t="n">
         <v>134383.9</v>
       </c>
-      <c r="H347" s="2" t="n">
+      <c r="H347" s="4" t="n">
         <v>10312.28</v>
       </c>
-      <c r="I347" s="2" t="n"/>
-      <c r="J347" s="2" t="n">
+      <c r="I347" s="4" t="n"/>
+      <c r="J347" s="4" t="n">
         <v>25097.85</v>
       </c>
-      <c r="K347" s="2" t="n">
+      <c r="K347" s="4" t="n">
         <v>39967.12</v>
       </c>
-      <c r="L347" s="2" t="n">
+      <c r="L347" s="4" t="n">
         <v>37337.16</v>
       </c>
-      <c r="M347" s="2" t="n">
+      <c r="M347" s="4" t="n">
         <v>31981.77</v>
       </c>
-      <c r="N347" s="2" t="n">
+      <c r="N347" s="4" t="n">
         <v>25631</v>
       </c>
-      <c r="O347" s="2" t="n">
+      <c r="O347" s="4" t="n">
         <v>25731</v>
       </c>
-      <c r="P347" t="inlineStr">
-        <is>
-          <t>digital</t>
+      <c r="P347" s="3" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="Q347" s="3" t="inlineStr">
+        <is>
+          <t>70.02 trim2: parent 39.967,12 != sum(children) 3.538,12 (2 children); 70.02 trim1: parent 25.097,85 != sum(children) 2.521,15 (2 children); 70.02 trim4: parent 31.981,77 != sum(children) 2.581,19 (2 children); 70.02 est2028: parent 25.731,00 != sum(children) 5.379,00 (2 children); 70.02 total: parent 134.383,90 != sum(children) 11.798,11 (2 children); 70.02 trim3: parent 37.337,16 != sum(children) 3.157,65 (2 children); 70.02 est2027: parent 25.631,00 != sum(children) 5.379,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -17390,7 +17401,7 @@
       </c>
       <c r="Q356" s="3" t="inlineStr">
         <is>
-          <t>10.03 total: parent 580,00 != sum(children) 280,00 (2 children); 10.03 trim1: parent 380,00 != sum(children) 280,00 (2 children)</t>
+          <t>10.03 trim1: parent 380,00 != sum(children) 280,00 (2 children); 10.03 total: parent 580,00 != sum(children) 280,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -19450,52 +19461,59 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr">
+      <c r="A399" s="3" t="inlineStr">
         <is>
           <t>84.02</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr">
+      <c r="B399" s="3" t="n"/>
+      <c r="C399" s="3" t="inlineStr">
         <is>
           <t>TRANSPORTURI</t>
         </is>
       </c>
-      <c r="E399" t="n">
+      <c r="D399" s="3" t="n"/>
+      <c r="E399" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="F399" t="inlineStr">
+      <c r="F399" s="3" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G399" s="2" t="n">
+      <c r="G399" s="4" t="n">
         <v>92544.17999999999</v>
       </c>
-      <c r="H399" s="2" t="n">
+      <c r="H399" s="4" t="n">
         <v>2853.01</v>
       </c>
-      <c r="I399" s="2" t="n"/>
-      <c r="J399" s="2" t="n">
+      <c r="I399" s="4" t="n"/>
+      <c r="J399" s="4" t="n">
         <v>24940.57</v>
       </c>
-      <c r="K399" s="2" t="n">
+      <c r="K399" s="4" t="n">
         <v>22806.28</v>
       </c>
-      <c r="L399" s="2" t="n">
+      <c r="L399" s="4" t="n">
         <v>22656.28</v>
       </c>
-      <c r="M399" s="2" t="n">
+      <c r="M399" s="4" t="n">
         <v>22141.05</v>
       </c>
-      <c r="N399" s="2" t="n">
+      <c r="N399" s="4" t="n">
         <v>7670</v>
       </c>
-      <c r="O399" s="2" t="n">
+      <c r="O399" s="4" t="n">
         <v>7720</v>
       </c>
-      <c r="P399" t="inlineStr">
-        <is>
-          <t>digital</t>
+      <c r="P399" s="3" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="Q399" s="3" t="inlineStr">
+        <is>
+          <t>84.02 trim2: parent 22.806,28 != sum(children) 6.826,00 (1 children); 84.02 trim1: parent 24.940,57 != sum(children) 16.294,42 (1 children); 84.02 trim4: parent 22.141,05 != sum(children) 6.824,09 (1 children); 84.02 total: parent 92.544,18 != sum(children) 36.770,51 (1 children); 84.02 trim3: parent 22.656,28 != sum(children) 6.826,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -40347,7 +40365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -40393,12 +40411,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -40411,24 +40429,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 30.02 est2027: still inconsistent — UNRESOLVED</t>
+          <t>30.02 trim2: parent 525,00 != sum(children) 225,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -40441,24 +40459,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 30.02 est2028: still inconsistent — UNRESOLVED</t>
+          <t>30.02 trim1: parent 525,00 != sum(children) 225,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -40471,24 +40489,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 30.02 total: still inconsistent — UNRESOLVED</t>
+          <t>30.02 trim4: parent 284,00 != sum(children) 159,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -40501,24 +40519,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 30.02 trim1: still inconsistent — UNRESOLVED</t>
+          <t>30.02 est2028: parent 1.670,00 != sum(children) 740,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -40531,24 +40549,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 30.02 trim2: still inconsistent — UNRESOLVED</t>
+          <t>30.02 total: parent 1.659,00 != sum(children) 734,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -40566,19 +40584,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 30.02 trim3: still inconsistent — UNRESOLVED</t>
+          <t>30.02 trim3: parent 325,00 != sum(children) 125,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -40591,24 +40609,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 30.02 trim4: still inconsistent — UNRESOLVED</t>
+          <t>30.02 est2027: parent 1.670,00 != sum(children) 740,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -40621,24 +40639,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LLM re-read 7 rows for 42.02 total: still inconsistent — UNRESOLVED</t>
+          <t>42.02 trim2: parent 49.487,32 != sum(children) 48.887,32 (6 children)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -40656,19 +40674,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LLM re-read 7 rows for 42.02 trim1: still inconsistent — UNRESOLVED</t>
+          <t>42.02 trim1: parent 26.936,76 != sum(children) 26.236,76 (6 children)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -40681,24 +40699,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LLM re-read 7 rows for 42.02 trim2: still inconsistent — UNRESOLVED</t>
+          <t>42.02 trim4: parent 43.950,70 != sum(children) 43.715,17 (6 children)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -40711,24 +40729,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LLM re-read 7 rows for 42.02 trim3: still inconsistent — UNRESOLVED</t>
+          <t>42.02 total: parent 166.103,28 != sum(children) 164.067,75 (6 children)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -40741,24 +40759,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LLM re-read 7 rows for 42.02 trim4: still inconsistent — UNRESOLVED</t>
+          <t>42.02 trim3: parent 45.728,50 != sum(children) 45.228,50 (6 children)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -40771,24 +40789,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 45.02 total: still inconsistent — UNRESOLVED</t>
+          <t>45.02 trim2: parent 0,00 != sum(children) 10.200,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -40806,19 +40824,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 45.02 trim1: still inconsistent — UNRESOLVED</t>
+          <t>45.02 trim1: parent 0,00 != sum(children) 10.200,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -40831,24 +40849,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 45.02 trim2: still inconsistent — UNRESOLVED</t>
+          <t>45.02 trim4: parent 0,00 != sum(children) 9.107,11 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -40861,24 +40879,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 45.02 trim3: still inconsistent — UNRESOLVED</t>
+          <t>45.02 total: parent 0,00 != sum(children) 39.707,11 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -40891,24 +40909,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 45.02 trim4: still inconsistent — UNRESOLVED</t>
+          <t>45.02 trim3: parent 0,00 != sum(children) 10.200,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -40921,24 +40939,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 51.02 total: sum now consistent — applied</t>
+          <t>51.02 trim2: parent 5.065,87 != sum(children) 45,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -40956,19 +40974,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 51.02 trim1: sum now consistent — applied</t>
+          <t>51.02 trim1: parent 5.355,64 != sum(children) 45,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -40981,24 +40999,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 51.02 trim2: sum now consistent — applied</t>
+          <t>51.02 trim4: parent 3.999,52 != sum(children) 36,40 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -41011,24 +41029,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 51.02 trim3: sum now consistent — applied</t>
+          <t>51.02 total: parent 18.987,40 != sum(children) 171,40 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -41041,24 +41059,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 51.02 trim4: sum now consistent — applied</t>
+          <t>51.02 trim3: parent 4.566,37 != sum(children) 45,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -41071,24 +41089,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 20.06 total: still inconsistent — UNRESOLVED</t>
+          <t>20.06 trim2: parent 17,00 != sum(children) 5,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -41101,24 +41119,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 20.06 trim2: still inconsistent — UNRESOLVED</t>
+          <t>20.06 total: parent 30,00 != sum(children) 5,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -41131,24 +41149,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 54.02 total: sum now consistent — applied</t>
+          <t>54.02 trim2: parent 2.596,30 != sum(children) 7,20 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -41161,19 +41179,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 54.02 trim2: sum now consistent — applied</t>
+          <t>54.02 total: parent 7.690,71 != sum(children) 7,20 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -41186,29 +41204,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 20 total: still inconsistent — UNRESOLVED</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -41226,27 +41239,27 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 20 trim1: still inconsistent — UNRESOLVED</t>
+          <t>20 trim1: parent 41,50 != sum(children) 40,50 (5 children)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -41256,19 +41269,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 61.02 total: sum now consistent — applied</t>
+          <t>20 total: parent 120,00 != sum(children) 119,00 (5 children)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -41276,29 +41289,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 61.02 trim2: sum now consistent — applied</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -41306,29 +41314,29 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LLM re-read 9 rows for 20.01 total: sum now consistent — applied</t>
+          <t>61.02 trim2: parent 1.329,50 != sum(children) 36,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -41336,29 +41344,29 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LLM re-read 9 rows for 20.01 trim1: sum now consistent — applied</t>
+          <t>61.02 total: parent 4.945,40 != sum(children) 36,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -41366,29 +41374,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20.01</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>LLM re-read 9 rows for 20.01 trim2: sum now consistent — applied</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -41401,24 +41404,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>LLM re-read 9 rows for 20.01 trim3: sum now consistent — applied</t>
+          <t>20.01 trim2: parent 80,75 != sum(children) 22,75 (8 children)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -41431,114 +41434,114 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>LLM re-read 9 rows for 20.01 trim4: sum now consistent — applied</t>
+          <t>20.01 trim1: parent 112,05 != sum(children) 53,95 (8 children)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>LLM re-read 7 rows for 65.02 est2027: sum now consistent — applied</t>
+          <t>20.01 trim4: parent 12,45 != sum(children) 2,05 (8 children)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>LLM re-read 7 rows for 65.02 est2028: sum now consistent — applied</t>
+          <t>20.01 total: parent 269,00 != sum(children) 87,00 (8 children)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LLM re-read 7 rows for 65.02 total: sum now consistent — applied</t>
+          <t>20.01 trim3: parent 63,75 != sum(children) 8,25 (8 children)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -41551,24 +41554,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LLM re-read 7 rows for 65.02 trim1: sum now consistent — applied</t>
+          <t>65.02 trim2: parent 8.485,84 != sum(children) 3.307,40 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -41581,24 +41584,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LLM re-read 7 rows for 65.02 trim2: sum now consistent — applied</t>
+          <t>65.02 trim1: parent 12.164,47 != sum(children) 3.350,53 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -41611,24 +41614,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>LLM re-read 7 rows for 65.02 trim3: sum now consistent — applied</t>
+          <t>65.02 trim4: parent 4.492,84 != sum(children) 3.041,14 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -41641,24 +41644,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LLM re-read 7 rows for 65.02 trim4: sum now consistent — applied</t>
+          <t>65.02 est2028: parent 8.036,62 != sum(children) 4.595,62 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -41666,7 +41669,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -41676,19 +41679,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LLM re-read 8 rows for 20.01 total: still inconsistent — UNRESOLVED</t>
+          <t>65.02 total: parent 30.818,07 != sum(children) 12.931,96 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -41696,29 +41699,29 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LLM re-read 8 rows for 20.01 trim1: still inconsistent — UNRESOLVED</t>
+          <t>65.02 trim3: parent 5.674,92 != sum(children) 3.232,89 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -41726,24 +41729,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LLM re-read 8 rows for 20.01 trim2: still inconsistent — UNRESOLVED</t>
+          <t>65.02 est2027: parent 8.506,62 != sum(children) 5.113,62 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -41756,67 +41759,62 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>20.01</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>trim3</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LLM re-read 8 rows for 20.01 trim3: still inconsistent — UNRESOLVED</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 20 total: still inconsistent — UNRESOLVED</t>
+          <t>20.01 trim2: parent 38,00 != sum(children) 36,00 (7 children)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -41826,74 +41824,74 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 20 trim1: still inconsistent — UNRESOLVED</t>
+          <t>20.01 trim1: parent 3.274,60 != sum(children) 3.150,72 (7 children)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 20 trim2: still inconsistent — UNRESOLVED</t>
+          <t>20.01 total: parent 3.349,60 != sum(children) 3.222,72 (7 children)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 67.02 est2027: still inconsistent — UNRESOLVED</t>
+          <t>20.01 trim3: parent 29,00 != sum(children) 28,00 (7 children)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -41902,71 +41900,66 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>est2028</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 67.02 est2028: still inconsistent — UNRESOLVED</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 67.02 total: still inconsistent — UNRESOLVED</t>
+          <t>20 trim2: parent 108,60 != sum(children) 99,60 (5 children)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -41976,49 +41969,49 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 67.02 trim1: still inconsistent — UNRESOLVED</t>
+          <t>20 trim1: parent 75,40 != sum(children) 74,40 (5 children)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 67.02 trim2: still inconsistent — UNRESOLVED</t>
+          <t>20 total: parent 200,00 != sum(children) 190,00 (5 children)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -42031,24 +42024,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 67.02 trim3: still inconsistent — UNRESOLVED</t>
+          <t>67.02 trim2: parent 6.404,85 != sum(children) 2.151,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -42061,212 +42054,212 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 67.02 trim4: still inconsistent — UNRESOLVED</t>
+          <t>67.02 trim1: parent 5.740,01 != sum(children) 563,14 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 20.04 total: still inconsistent — UNRESOLVED</t>
+          <t>67.02 trim4: parent 1.404,72 != sum(children) 305,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 20.04 trim1: still inconsistent — UNRESOLVED</t>
+          <t>67.02 est2028: parent 17.470,00 != sum(children) 3.990,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 20.04 trim2: still inconsistent — UNRESOLVED</t>
+          <t>67.02 total: parent 16.359,72 != sum(children) 4.235,15 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 70.02 est2027: sum now consistent — applied</t>
+          <t>67.02 trim3: parent 2.810,14 != sum(children) 1.216,01 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 70.02 est2028: sum now consistent — applied</t>
+          <t>67.02 est2027: parent 17.180,00 != sum(children) 3.890,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 70.02 total: sum now consistent — applied</t>
+          <t>67.02 trim2: parent 6.404,85 != sum(children) 677,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -42276,104 +42269,99 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 70.02 trim1: sum now consistent — applied</t>
+          <t>67.02 trim1: parent 5.740,01 != sum(children) 47,14 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 70.02 trim2: sum now consistent — applied</t>
+          <t>67.02 trim3: parent 2.810,14 != sum(children) 120,01 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 70.02 trim3: sum now consistent — applied</t>
+          <t>67.02 total: parent 16.359,72 != sum(children) 844,15 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>trim4</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 70.02 trim4: sum now consistent — applied</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -42382,131 +42370,126 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10.03</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 10.03 total: still inconsistent — UNRESOLVED</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>20.04</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 10.03 trim1: still inconsistent — UNRESOLVED</t>
+          <t>20.04 trim2: parent 9,00 != sum(children) 8,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>20.04</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 total: sum now consistent — applied</t>
+          <t>20.04 trim1: parent 19,00 != sum(children) 8,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>20.04</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 trim1: sum now consistent — applied</t>
+          <t>20.04 total: parent 29,00 != sum(children) 17,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -42516,57 +42499,57 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 trim2: sum now consistent — applied</t>
+          <t>70.02 trim2: parent 39.967,12 != sum(children) 3.538,12 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 trim3: sum now consistent — applied</t>
+          <t>70.02 trim1: parent 25.097,85 != sum(children) 2.521,15 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -42576,7 +42559,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 trim4: sum now consistent — applied</t>
+          <t>70.02 trim4: parent 31.981,77 != sum(children) 2.581,19 (2 children)</t>
         </is>
       </c>
     </row>
@@ -42592,11 +42575,11 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -42606,7 +42589,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>30.02 est2028: parent 1.670,00 != sum(children) 740,00 (2 children)</t>
+          <t>70.02 est2028: parent 25.731,00 != sum(children) 5.379,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -42622,21 +42605,21 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>30.02 est2027: parent 1.670,00 != sum(children) 740,00 (2 children)</t>
+          <t>70.02 total: parent 134.383,90 != sum(children) 11.798,11 (2 children)</t>
         </is>
       </c>
     </row>
@@ -42652,21 +42635,21 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>30.02 trim4: parent 284,00 != sum(children) 159,00 (2 children)</t>
+          <t>70.02 trim3: parent 37.337,16 != sum(children) 3.157,65 (2 children)</t>
         </is>
       </c>
     </row>
@@ -42682,51 +42665,46 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>30.02 total: parent 1.659,00 != sum(children) 734,00 (2 children)</t>
+          <t>70.02 est2027: parent 25.631,00 != sum(children) 5.379,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>30.02</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>30.02 trim2: parent 525,00 != sum(children) 225,00 (2 children)</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -42742,21 +42720,21 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>30.02 trim3: parent 325,00 != sum(children) 125,00 (2 children)</t>
+          <t>10.03 trim1: parent 380,00 != sum(children) 280,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -42772,21 +42750,21 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>30.02 trim1: parent 525,00 != sum(children) 225,00 (2 children)</t>
+          <t>10.03 total: parent 580,00 != sum(children) 280,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -42802,21 +42780,21 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>42.02 trim4: parent 43.950,70 != sum(children) 43.715,17 (6 children)</t>
+          <t>84.02 trim2: parent 22.806,28 != sum(children) 6.826,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -42832,21 +42810,21 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>42.02 total: parent 166.103,28 != sum(children) 164.067,75 (6 children)</t>
+          <t>84.02 trim1: parent 24.940,57 != sum(children) 16.294,42 (1 children)</t>
         </is>
       </c>
     </row>
@@ -42862,21 +42840,21 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>42.02 trim2: parent 49.487,32 != sum(children) 48.887,32 (6 children)</t>
+          <t>84.02 trim4: parent 22.141,05 != sum(children) 6.824,09 (1 children)</t>
         </is>
       </c>
     </row>
@@ -42892,21 +42870,21 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>42.02 trim3: parent 45.728,50 != sum(children) 45.228,50 (6 children)</t>
+          <t>84.02 total: parent 92.544,18 != sum(children) 36.770,51 (1 children)</t>
         </is>
       </c>
     </row>
@@ -42922,58 +42900,53 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>42.02 trim1: parent 26.936,76 != sum(children) 26.236,76 (6 children)</t>
+          <t>84.02 trim3: parent 22.656,28 != sum(children) 6.826,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>45.02</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>trim4</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>45.02 trim4: parent 0,00 != sum(children) 9.107,11 (1 children)</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -42982,171 +42955,141 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>45.02</t>
-        </is>
+        <v>15</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>45.02 total: parent 0,00 != sum(children) 39.707,11 (1 children)</t>
+          <t>unparseable cell '1=3+4+5+6' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>45.02</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>45.02 trim2: parent 0,00 != sum(children) 10.200,00 (1 children)</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>45.02</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>trim3</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>45.02 trim3: parent 0,00 != sum(children) 10.200,00 (1 children)</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>45.02</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>45.02 trim1: parent 0,00 != sum(children) 10.200,00 (1 children)</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>20.06</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>20.06 total: parent 30,00 != sum(children) 5,00 (1 children)</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>20.06</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>20.06 trim2: parent 17,00 != sum(children) 5,00 (1 children)</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -43162,7 +43105,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -43178,60 +43121,50 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>20 total: parent 120,00 != sum(children) 119,00 (5 children)</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>20 trim1: parent 41,50 != sum(children) 40,50 (5 children)</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -43247,7 +43180,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -43266,1135 +43199,20 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>01</t>
+        <v>30</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>7</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>7</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>20.01</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>20.01 total: parent 3.349,60 != sum(children) 3.222,72 (7 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>7</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>20.01</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>trim2</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>20.01 trim2: parent 38,00 != sum(children) 36,00 (7 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>7</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>20.01</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>trim3</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>20.01 trim3: parent 29,00 != sum(children) 28,00 (7 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>7</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>20.01</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>trim1</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>20.01 trim1: parent 3.274,60 != sum(children) 3.150,72 (7 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>9</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>9</v>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>20 total: parent 200,00 != sum(children) 190,00 (5 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>9</v>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>trim1</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>20 trim1: parent 75,40 != sum(children) 74,40 (5 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>9</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>trim2</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>20 trim2: parent 108,60 != sum(children) 99,60 (5 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>10</v>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>est2028</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>67.02 est2028: parent 17.470,00 != sum(children) 3.990,00 (3 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>10</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>est2027</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>67.02 est2027: parent 17.180,00 != sum(children) 3.890,00 (3 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>10</v>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>trim4</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>67.02 trim4: parent 1.404,72 != sum(children) 305,00 (3 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>10</v>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>67.02 total: parent 16.359,72 != sum(children) 4.235,15 (3 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>10</v>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>trim2</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>67.02 trim2: parent 6.404,85 != sum(children) 2.151,00 (3 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>10</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>trim3</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>67.02 trim3: parent 2.810,14 != sum(children) 1.216,01 (3 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>10</v>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>trim1</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>67.02 trim1: parent 5.740,01 != sum(children) 563,14 (3 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>10</v>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>trim3</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>67.02 trim3: parent 2.810,14 != sum(children) 120,01 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>10</v>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>67.02 total: parent 16.359,72 != sum(children) 844,15 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>10</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>trim1</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>67.02 trim1: parent 5.740,01 != sum(children) 47,14 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>10</v>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>trim2</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>67.02 trim2: parent 6.404,85 != sum(children) 677,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>10</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>11</v>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>11</v>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>20.04</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>20.04 total: parent 29,00 != sum(children) 17,00 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>11</v>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>20.04</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>trim1</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>20.04 trim1: parent 19,00 != sum(children) 8,00 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>11</v>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>20.04</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>trim2</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>20.04 trim2: parent 9,00 != sum(children) 8,00 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>12</v>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>12</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>10.03</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>10.03 total: parent 580,00 != sum(children) 280,00 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>12</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>10.03</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>trim1</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>10.03 trim1: parent 380,00 != sum(children) 280,00 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>14</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>15</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>unparseable cell '1=3+4+5+6' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>20</v>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>21</v>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>21</v>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>22</v>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>24</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>25</v>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>26</v>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>27</v>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>29</v>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>duplicate of p4 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>30</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
         <is>
           <t>unparseable cell '1=3+4+5+6' in column total_2026</t>
         </is>
@@ -44411,7 +43229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -44433,7 +43251,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -44443,72 +43261,230 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>829</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>801</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>96.59999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46</v>
+        <v>829</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58</v>
+        <v>794</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Modele LLM folosite</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gemini-3.6-flash</t>
-        </is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>95.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4115</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3877</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>94.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>b16e301d2c7e6b35af3498f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>edc67cb5238edcb4f9d5bb56eb78bcc406d8a851ffd03dd26c0e325f989f03d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
           <t>— BUGETUL LOCAL PE ANUL</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>local, pag. 1-30, 836 linii</t>
         </is>
